--- a/Project_Tasks.xlsx
+++ b/Project_Tasks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\DewanSoftTask\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D62F5DF-9441-4509-B6AC-1B84F404832E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8099B67-BB0D-4C71-9EEA-8A6E3D7171E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Task Title</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Priority</t>
-  </si>
-  <si>
     <t>Implement Stock Validation</t>
   </si>
   <si>
@@ -85,12 +82,6 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>Set up ASP.NET Core project with dependencies (Entity Framework, MySQL, etc.). Initialize and configure the project.</t>
   </si>
   <si>
@@ -112,10 +103,10 @@
     <t xml:space="preserve">30 minutes	</t>
   </si>
   <si>
-    <t>Create Controllers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implemented the controllers to handle logic and user interactions for receipts and items.	</t>
+    <t>Implemented service-based controllers to manage logic and user interactions for receipts and items, leveraging dedicated service layers for clean and maintainable architecture</t>
+  </si>
+  <si>
+    <t>Create Services and Controllers</t>
   </si>
 </sst>
 </file>
@@ -487,8 +478,8 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.88671875" customWidth="1"/>
-    <col min="2" max="2" width="98.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.77734375" customWidth="1"/>
+    <col min="2" max="2" width="146.44140625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="10.88671875" customWidth="1"/>
@@ -514,16 +505,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2">
         <v>45651</v>
@@ -532,21 +521,18 @@
         <v>45651</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2">
         <v>45651</v>
@@ -555,21 +541,18 @@
         <v>45651</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2">
         <v>45651</v>
@@ -578,21 +561,18 @@
         <v>45651</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2">
         <v>45652</v>
@@ -601,21 +581,18 @@
         <v>45652</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2">
         <v>45652</v>
@@ -624,21 +601,18 @@
         <v>45652</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2">
         <v>45652</v>
@@ -647,21 +621,18 @@
         <v>45652</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2">
         <v>45652</v>
@@ -670,21 +641,18 @@
         <v>45652</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2">
         <v>45652</v>
@@ -693,21 +661,18 @@
         <v>45652</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2">
         <v>45653</v>
@@ -716,13 +681,10 @@
         <v>45653</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Project_Tasks.xlsx
+++ b/Project_Tasks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\GitHub\DewanSoftTask\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Aya\Api\DewanSoftTask\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8099B67-BB0D-4C71-9EEA-8A6E3D7171E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49753A77-031A-47B5-AA43-A8B34BF0E87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>Task Title</t>
   </si>
@@ -28,15 +28,6 @@
     <t>Task Description</t>
   </si>
   <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -70,15 +61,6 @@
     <t>Prepare the ERD diagram and project documentation.</t>
   </si>
   <si>
-    <t>2 hours</t>
-  </si>
-  <si>
-    <t>3 hours</t>
-  </si>
-  <si>
-    <t>1 hour</t>
-  </si>
-  <si>
     <t>Completed</t>
   </si>
   <si>
@@ -98,9 +80,6 @@
   </si>
   <si>
     <t>Add migration to create database tables and verify the database schema in MySQL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 minutes	</t>
   </si>
   <si>
     <t>Implemented service-based controllers to manage logic and user interactions for receipts and items, leveraging dedicated service layers for clean and maintainable architecture</t>
@@ -165,12 +144,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,18 +453,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
     <col min="2" max="2" width="146.44140625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,195 +471,105 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45651</v>
-      </c>
-      <c r="D2" s="2">
-        <v>45651</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45651</v>
-      </c>
-      <c r="D3" s="2">
-        <v>45651</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45651</v>
-      </c>
-      <c r="D4" s="2">
-        <v>45651</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45652</v>
-      </c>
-      <c r="D5" s="2">
-        <v>45652</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2">
-        <v>45652</v>
-      </c>
-      <c r="D6" s="2">
-        <v>45652</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2">
-        <v>45652</v>
-      </c>
-      <c r="D7" s="2">
-        <v>45652</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2">
-        <v>45652</v>
-      </c>
-      <c r="D8" s="2">
-        <v>45652</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2">
-        <v>45652</v>
-      </c>
-      <c r="D9" s="2">
-        <v>45652</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2">
-        <v>45653</v>
-      </c>
-      <c r="D10" s="2">
-        <v>45653</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
+      <c r="C10" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
